--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="252">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T12:52:51+00:00</t>
+    <t>2025-02-24T13:32:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,10 +311,6 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
-</t>
   </si>
   <si>
     <t>LegalAuthenticator.typeId.nullFlavor</t>
@@ -1662,7 +1658,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1670,10 +1666,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1771,39 +1767,39 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1854,7 +1850,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1874,39 +1870,39 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1957,7 +1953,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1977,39 +1973,39 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K9" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2018,49 +2014,49 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2080,17 +2076,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -2108,11 +2104,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2163,7 +2159,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2183,10 +2179,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2213,7 +2209,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2264,7 +2260,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2284,10 +2280,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2321,7 +2317,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -2343,7 +2339,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2361,7 +2357,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2381,10 +2377,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2418,7 +2414,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2440,7 +2436,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2458,7 +2454,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2478,10 +2474,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2504,10 +2500,10 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2559,7 +2555,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2579,10 +2575,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2680,10 +2676,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2706,13 +2702,13 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2763,7 +2759,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2783,10 +2779,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2812,7 +2808,7 @@
         <v>91</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
@@ -2844,37 +2840,37 @@
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>74</v>
@@ -2882,10 +2878,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2983,10 +2979,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3015,7 +3011,7 @@
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3066,7 +3062,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3086,17 +3082,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>80</v>
@@ -3114,11 +3110,11 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3169,7 +3165,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3189,17 +3185,17 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>80</v>
@@ -3217,11 +3213,11 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3272,7 +3268,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3292,17 +3288,17 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>80</v>
@@ -3320,11 +3316,11 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3375,7 +3371,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3395,17 +3391,17 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>80</v>
@@ -3423,11 +3419,11 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3478,7 +3474,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3498,10 +3494,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3524,11 +3520,11 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3579,7 +3575,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3599,10 +3595,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3625,11 +3621,11 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3680,7 +3676,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3700,39 +3696,39 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K26" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="F26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K26" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3783,7 +3779,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3803,39 +3799,39 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E27" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K27" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="F27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K27" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3886,7 +3882,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3906,39 +3902,39 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E28" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K28" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="F28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K28" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3989,7 +3985,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4009,10 +4005,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4035,11 +4031,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4090,7 +4086,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4110,10 +4106,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4136,10 +4132,10 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
@@ -4191,7 +4187,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -4211,10 +4207,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4312,10 +4308,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4413,10 +4409,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4506,7 +4502,7 @@
         <v>74</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>74</v>
@@ -4514,10 +4510,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4615,39 +4611,39 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E35" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K35" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4698,7 +4694,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4718,39 +4714,39 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E36" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K36" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K36" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4801,7 +4797,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4821,39 +4817,39 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K37" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K37" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4862,49 +4858,49 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4924,17 +4920,17 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>75</v>
@@ -4952,11 +4948,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5007,7 +5003,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5027,10 +5023,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5057,7 +5053,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5108,7 +5104,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5128,10 +5124,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5165,7 +5161,7 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>74</v>
@@ -5187,25 +5183,25 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5225,10 +5221,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5254,7 +5250,7 @@
         <v>95</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
@@ -5306,7 +5302,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -5326,10 +5322,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5427,39 +5423,39 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K43" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5510,7 +5506,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5530,39 +5526,39 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K44" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5613,7 +5609,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5633,41 +5629,41 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K45" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="F45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>112</v>
-      </c>
       <c r="L45" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5718,7 +5714,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5738,41 +5734,41 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E46" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="F46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="F46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5823,7 +5819,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -5843,10 +5839,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5869,7 +5865,7 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -5922,7 +5918,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -5942,10 +5938,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5968,10 +5964,10 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -6003,25 +5999,25 @@
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6041,10 +6037,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6142,10 +6138,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6174,7 +6170,7 @@
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6225,7 +6221,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6245,17 +6241,17 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
@@ -6273,11 +6269,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6328,7 +6324,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6348,17 +6344,17 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>80</v>
@@ -6376,11 +6372,11 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6431,7 +6427,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6451,17 +6447,17 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>80</v>
@@ -6479,11 +6475,11 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6534,7 +6530,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6554,17 +6550,17 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>80</v>
@@ -6582,11 +6578,11 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6637,7 +6633,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6657,10 +6653,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6683,11 +6679,11 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6738,7 +6734,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -6758,10 +6754,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6784,11 +6780,11 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -6839,7 +6835,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -6859,39 +6855,39 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E57" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="F57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K57" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="F57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -6942,7 +6938,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -6962,39 +6958,39 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E58" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="F58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K58" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="F58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7045,7 +7041,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7065,17 +7061,17 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>80</v>
@@ -7093,11 +7089,11 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7148,7 +7144,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7168,10 +7164,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7194,10 +7190,10 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
@@ -7249,7 +7245,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7269,10 +7265,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7295,10 +7291,10 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
@@ -7350,7 +7346,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7370,10 +7366,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7396,10 +7392,10 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
@@ -7451,7 +7447,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7471,10 +7467,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7497,10 +7493,10 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
@@ -7552,7 +7548,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7572,10 +7568,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7598,7 +7594,7 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -7651,7 +7647,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7671,10 +7667,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7750,7 +7746,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:32:36+00:00</t>
+    <t>2025-02-24T13:36:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:36:50+00:00</t>
+    <t>2025-03-04T16:07:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T16:07:16+00:00</t>
+    <t>2025-03-06T10:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T10:23:19+00:00</t>
+    <t>2025-03-10T13:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T13:00:25+00:00</t>
+    <t>2025-03-11T15:29:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T13:18:22+00:00</t>
+    <t>2025-03-14T15:47:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:47:10+00:00</t>
+    <t>2025-03-25T13:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>legalAuthenticator</t>
+    <t>CDA - legalAuthenticator</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1107,42 +1107,42 @@
   <dimension ref="A1:AK65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="62.19140625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="62.19140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="24.9375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="53.31640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="53.31640625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="21.37890625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="151.96875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="130.28515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="97.74609375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.20703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="83.80078125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.75390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:06:14+00:00</t>
+    <t>2025-04-28T09:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:53:39+00:00</t>
+    <t>2025-05-06T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:44:46+00:00</t>
+    <t>2025-05-06T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:53:54+00:00</t>
+    <t>2025-05-06T15:58:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:58:22+00:00</t>
+    <t>2025-05-20T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T10:20:09+00:00</t>
+    <t>2025-05-20T12:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
